--- a/Dashboards/data/Data final/empleo/empleo adecuado/empleo_scorecard.xlsx
+++ b/Dashboards/data/Data final/empleo/empleo adecuado/empleo_scorecard.xlsx
@@ -98,7 +98,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>3.0951061248779297</v>
+        <v>2.6120502948760986</v>
       </c>
     </row>
     <row r="3">
@@ -109,7 +109,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="1">
-        <v>36.767078399658203</v>
+        <v>37.068805694580078</v>
       </c>
     </row>
     <row r="4">
@@ -120,7 +120,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="1">
-        <v>60.137813568115234</v>
+        <v>60.319145202636719</v>
       </c>
     </row>
   </sheetData>
